--- a/forms/trg/Formulir_TRG_mhsrg.xlsx
+++ b/forms/trg/Formulir_TRG_mhsrg.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -686,114 +686,126 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>Belum ada proyek riset tercatat di situs.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Nama</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Nama</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
+          <t>SINTA ID</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>6012345</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
           <t>ORCID</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Kemajuan pengisian (otomatis)</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>Anggota tercantum</t>
-        </is>
-      </c>
-      <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B29)</f>
-        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
+          <t>Anggota tercantum</t>
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F29)</f>
+        <f>COUNTA(Anggota!B5:B30)</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
+          <t>Anggota dengan keahlian terpilih</t>
+        </is>
+      </c>
+      <c r="B26" s="7">
+        <f>COUNTA(Anggota!F5:F30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B26" s="8">
-        <f>IF(B24=0,0,B25/B24)</f>
+      <c r="B27" s="8">
+        <f>IF(B25=0,0,B26/B25)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,33 +925,29 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Atika Puspita Marzaman, S.IP., MA</t>
+          <t>Nur Isdah Idris, S.IP., MA., Ph.D</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>International Organizations and Regimes</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Refugee and Forced Migration, Human Right Law, and International Community Development</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-9152-1875</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
@@ -954,17 +962,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Andi Ahmad Hasan Tenriliweng, S.ST., M.Si</t>
+          <t>Atika Puspita Marzaman, S.IP., MA</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>International Organizations and Regimes</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -978,7 +986,7 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0009-0008-5618-1169</t>
+          <t>0009-0009-9152-1875</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
@@ -995,29 +1003,33 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. L.G.H. (Laurens) Bakker</t>
+          <t>Dr. Andi Ahmad Hasan Tenriliweng, S.ST., M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Law and Justice, Resource Conflict, Discourses of Authority and Non-State Violence</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Leiden University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0008-5618-1169</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
@@ -1032,18 +1044,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Tarikhul Haq, S.IP., MA</t>
+          <t>Dr. L.G.H. (Laurens) Bakker</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n"/>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>Law and Justice, Resource Conflict, Discourses of Authority and Non-State Violence</t>
+        </is>
+      </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Inclusive Development, Community Resilience and Disability-Inclusive Climate Adaptation</t>
+          <t>Leiden University</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1065,18 +1081,18 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Amdya Hisyam, S.IP., MA</t>
+          <t>Ahmad Tarikhul Haq, S.IP., MA</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Inclusive Development, Community Resilience and Disability-Inclusive Climate Adaptation</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1098,33 +1114,25 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Munif Arif Ranti, S.IP., MA</t>
+          <t>Amdya Hisyam, S.IP., MA</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Human Security and Environmental Politics</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-2415-3007</t>
-        </is>
-      </c>
+      <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
@@ -1139,17 +1147,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Fajhriyadi Hastira, S.IP., M.H.I</t>
+          <t>Munif Arif Ranti, S.IP., MA</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Human Right</t>
+          <t>Human Security and Environmental Politics</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1163,7 +1171,7 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-0900-0782</t>
+          <t>0000-0002-2415-3007</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
@@ -1180,29 +1188,33 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Rasyiqa Fairuz R. Laitupa</t>
+          <t>Muhammad Fajhriyadi Hastira, S.IP., M.H.I</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>International Relations</t>
+          <t>Human Right</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Hasanuddin</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
       <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>0000-0002-0900-0782</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="11" t="inlineStr">
@@ -1217,12 +1229,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Rifqah Asrianti HR</t>
+          <t>Rasyiqa Fairuz R. Laitupa</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1254,12 +1266,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Iftitah Azzahra M.</t>
+          <t>Rifqah Asrianti HR</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1291,12 +1303,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Andi Muh. Guttu Patalo Zulkarnain</t>
+          <t>Iftitah Azzahra M.</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1328,22 +1340,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Al Fitrah Arysuci</t>
+          <t>Andi Muh. Guttu Patalo Zulkarnain</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>International Cooperation and Sustainable Development</t>
+          <t>International Relations</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Universitas Hasanuddin</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1365,17 +1377,17 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Cantika Venezia Wahid</t>
+          <t>Al Fitrah Arysuci</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>International Relations</t>
+          <t>International Cooperation and Sustainable Development</t>
         </is>
       </c>
       <c r="E17" s="11" t="inlineStr">
@@ -1400,10 +1412,26 @@
       <c r="A18" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="11" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Cantika Venezia Wahid</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Migration and Human Security Research Group (MHSRG) under the Thematic Research Group (TRG) of Hasanuddin University provides an important academic platform for advancing interdisciplinary research on forced migration, social cohesion, and human security.</t>
+        </is>
+      </c>
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
@@ -1411,7 +1439,11 @@
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1600,15 +1632,32 @@
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="12" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
